--- a/custom/demo/test/sample-input-data/accidental_discovery_and_epidemic/demo-analyses SALIOU.XLSX
+++ b/custom/demo/test/sample-input-data/accidental_discovery_and_epidemic/demo-analyses SALIOU.XLSX
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$H$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
     <author>Vincent Laugier</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0">
+    <comment ref="D2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="0">
+    <comment ref="D23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C24" authorId="0">
+    <comment ref="D24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C25" authorId="0">
+    <comment ref="D25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="17">
   <si>
     <t xml:space="preserve">patient_ref</t>
   </si>
@@ -89,6 +89,9 @@
     <t xml:space="preserve">analysis_ref</t>
   </si>
   <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
     <t xml:space="preserve">request_time</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t xml:space="preserve">result_raw_text</t>
   </si>
   <si>
+    <t xml:space="preserve">done</t>
+  </si>
+  <si>
     <t xml:space="preserve">stool</t>
   </si>
   <si>
@@ -117,6 +123,15 @@
   </si>
   <si>
     <t xml:space="preserve">positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bacterial_culture_vancomycin_resistant_enterococcus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requested</t>
   </si>
 </sst>
 </file>
@@ -211,7 +226,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -238,6 +253,10 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -384,17 +403,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="57.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="57.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="25.66"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,844 +441,965 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>44683</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>44682</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>44689.7083333333</v>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>44689.7083333333</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E3" s="4" t="n">
+        <v>44689.7083333333</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>44691</v>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E4" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>44691</v>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>44691</v>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>44691</v>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>44691</v>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>44691</v>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>44691</v>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>44691</v>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>44691</v>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>44691</v>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>44691</v>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>44691</v>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>44691</v>
+      <c r="C16" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>44691</v>
+      <c r="C17" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>44691</v>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>44691</v>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>44691</v>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>44691</v>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>44691</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>44692</v>
+      <c r="C22" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>44692</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="4" t="n">
+        <v>44692</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>44693</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>44692</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>44693</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>44692</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>44695</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>44694</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>44697</v>
+      <c r="C26" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>44697</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="4" t="n">
+        <v>44697</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="4" t="n">
-        <v>44698</v>
+      <c r="C27" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>44698</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="4" t="n">
+        <v>44698</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>44701</v>
+      <c r="C28" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>44701</v>
+      <c r="C29" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>44701</v>
+      <c r="C30" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>44701</v>
+      <c r="C31" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="4" t="n">
-        <v>44701</v>
+      <c r="C32" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>44701</v>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="4" t="n">
-        <v>44701</v>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>44701</v>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>44701</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="4" t="n">
-        <v>44713</v>
+      <c r="C36" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>44713</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="E36" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>44691</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>44701</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:I37"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/custom/demo/test/sample-input-data/accidental_discovery_and_epidemic/demo-analyses SALIOU.XLSX
+++ b/custom/demo/test/sample-input-data/accidental_discovery_and_epidemic/demo-analyses SALIOU.XLSX
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$I$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$I$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -226,7 +226,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -253,10 +253,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1372,7 +1368,7 @@
       <c r="F37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1393,13 +1389,13 @@
       <c r="F38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I37"/>
+  <autoFilter ref="A1:I38"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
